--- a/astro-site/public/dl/food-truck-checklist-templates/01-food-truck-setup-teardown-checklist.xlsx
+++ b/astro-site/public/dl/food-truck-checklist-templates/01-food-truck-setup-teardown-checklist.xlsx
@@ -776,7 +776,7 @@
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="inlineStr"/>
     </row>
-    <row r="12" ht="41" customHeight="1">
+    <row r="12" ht="54.5" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
@@ -784,7 +784,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Plug in cold equipment (cooler, refrigerated prep table): 41 °F or below, frozen 0 °F or below (FDA Food Code 3-501.16) — log reading: ____ °F</t>
+          <t>Plug in cold equipment (cooler, refrigerated prep table): 41 °F or below (FDA Food Code 3-501.16); frozen food stays frozen (0 °F or below is the common target) — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
